--- a/2026/ANATOLE FRANCE/Julio/ANATOLE-Julio.xlsx
+++ b/2026/ANATOLE FRANCE/Julio/ANATOLE-Julio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862CFC98-F664-479A-99B5-5D4F59802A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3E7834-0741-4081-B2E2-18F57BD6CDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="167">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -472,27 +477,9 @@
     <t>Fracchia garcia Sebastian ezequiel</t>
   </si>
   <si>
-    <t>Transf 06/05</t>
-  </si>
-  <si>
-    <t>Transf 11/05</t>
-  </si>
-  <si>
-    <t>Transf 12/05</t>
-  </si>
-  <si>
     <t>Barreiro Cristina</t>
   </si>
   <si>
-    <t>Transf 04/06</t>
-  </si>
-  <si>
-    <t>Inombiliaria Peduto - Honorarios (Sr. Vazquez Andres)</t>
-  </si>
-  <si>
-    <t>Transf 24/06</t>
-  </si>
-  <si>
     <t>German Meilinger</t>
   </si>
   <si>
@@ -517,25 +504,34 @@
     <t>Casa Ruan - Compra de materiales electricos</t>
   </si>
   <si>
-    <t>Transf 10/07</t>
-  </si>
-  <si>
     <t>Transf 06/07</t>
   </si>
   <si>
-    <t>Mozart SRL - Recarga de matafuegos</t>
-  </si>
-  <si>
     <t>Transf 02/07</t>
   </si>
   <si>
-    <t>Transf 29/06</t>
-  </si>
-  <si>
     <t>Doartero julio - Colocacion de llave de paso : Mano de obra y materiales</t>
   </si>
   <si>
     <t>Transf 21/07</t>
+  </si>
+  <si>
+    <t>Mozart SRL - Recarga de matafuegos - Señalizaciones, pruebas hidraulicas, etc</t>
+  </si>
+  <si>
+    <t>Transf 13/07</t>
+  </si>
+  <si>
+    <t>Transf 15/07</t>
+  </si>
+  <si>
+    <t>Destapaciones Roman: Destapacion columna ramal cocinas desde 6C hasta 3er piso</t>
+  </si>
+  <si>
+    <t>Transf 27/07</t>
+  </si>
+  <si>
+    <t>Deposito sin identificar 13/07</t>
   </si>
 </sst>
 </file>
@@ -553,7 +549,7 @@
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -760,6 +756,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1242,7 +1245,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1478,9 +1481,6 @@
     <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1500,137 +1500,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1639,6 +1512,137 @@
     </xf>
     <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="27" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1717,9 +1721,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1757,9 +1761,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1792,9 +1796,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1827,9 +1848,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2004,30 +2042,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="189" t="s">
+      <c r="B1" s="201" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="62" t="s">
         <v>26</v>
@@ -2036,16 +2074,16 @@
       <c r="D2" s="62"/>
       <c r="E2" s="63"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="190" t="s">
+      <c r="B3" s="202" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="191"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="203"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2056,12 +2094,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="62" t="s">
@@ -2069,7 +2107,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>56</v>
       </c>
@@ -2080,57 +2118,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="186" t="s">
-        <v>158</v>
-      </c>
-      <c r="C8" s="186"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="186"/>
-      <c r="C9" s="186"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="186"/>
-      <c r="C10" s="186"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="192" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="200" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="200"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="204" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="192"/>
-      <c r="C13" s="192"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="192"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="192"/>
-      <c r="B14" s="192"/>
-      <c r="C14" s="192"/>
-      <c r="D14" s="192"/>
-      <c r="E14" s="192"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
-      <c r="B15" s="192"/>
-      <c r="C15" s="192"/>
-      <c r="D15" s="192"/>
-      <c r="E15" s="192"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="192"/>
-      <c r="B16" s="192"/>
-      <c r="C16" s="192"/>
-      <c r="D16" s="192"/>
-      <c r="E16" s="192"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="204"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="204"/>
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="204"/>
+      <c r="B15" s="204"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="204"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2139,7 +2177,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>31</v>
       </c>
@@ -2148,18 +2186,18 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="187" t="s">
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="195" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="188"/>
+      <c r="B22" s="196"/>
       <c r="C22" s="5"/>
       <c r="D22" s="159">
         <v>1719538.75</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="70" t="s">
         <v>112</v>
       </c>
@@ -2170,7 +2208,7 @@
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="70" t="s">
         <v>113</v>
       </c>
@@ -2181,7 +2219,7 @@
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="54" t="s">
         <v>32</v>
       </c>
@@ -2194,7 +2232,7 @@
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
@@ -2203,28 +2241,28 @@
       <c r="D26" s="159"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="159"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="159"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="161"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>36</v>
       </c>
@@ -2233,7 +2271,7 @@
       <c r="D30" s="161"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54" t="s">
         <v>32</v>
       </c>
@@ -2245,7 +2283,7 @@
       </c>
       <c r="E31" s="102"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
         <v>1</v>
       </c>
@@ -2258,7 +2296,7 @@
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>18</v>
       </c>
@@ -2267,33 +2305,33 @@
       <c r="D33" s="164"/>
       <c r="E33" s="104"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="193" t="s">
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="191" t="s">
         <v>132</v>
       </c>
-      <c r="B34" s="194"/>
+      <c r="B34" s="192"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="231">
+      <c r="D34" s="187">
         <v>50000</v>
       </c>
-      <c r="E34" s="183" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="193" t="s">
-        <v>161</v>
-      </c>
-      <c r="B35" s="194"/>
+      <c r="E34" s="113" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="191" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" s="192"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="229">
+      <c r="D35" s="185">
         <v>190000</v>
       </c>
-      <c r="E35" s="184" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E35" s="113" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
         <v>15</v>
       </c>
@@ -2305,7 +2343,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
         <v>29</v>
       </c>
@@ -2314,20 +2352,20 @@
       <c r="D37" s="166"/>
       <c r="E37" s="105"/>
     </row>
-    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="187" t="s">
+    <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="195" t="s">
         <v>142</v>
       </c>
-      <c r="B38" s="188"/>
+      <c r="B38" s="196"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="167">
+      <c r="D38" s="188">
         <v>161303</v>
       </c>
       <c r="E38" s="119" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
         <v>2</v>
       </c>
@@ -2339,45 +2377,45 @@
         <v>161303</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
         <v>16</v>
       </c>
       <c r="B40" s="107"/>
       <c r="C40" s="107"/>
-      <c r="D40" s="168"/>
+      <c r="D40" s="167"/>
       <c r="E40" s="108"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="51"/>
-      <c r="D41" s="230">
+      <c r="D41" s="186">
         <v>1034496.5</v>
       </c>
       <c r="E41" s="113" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="G41" s="89"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="228">
+      <c r="D42" s="184">
         <v>77379.5</v>
       </c>
       <c r="E42" s="113" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="str">
         <f>A42</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2386,15 +2424,15 @@
         <v>110</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="228">
+      <c r="D43" s="184">
         <v>148088.01999999999</v>
       </c>
       <c r="E43" s="114" t="str">
         <f>E42</f>
-        <v>Transf 12/05</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Transf 13/07</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2403,87 +2441,87 @@
         <v>109</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="228">
+      <c r="D44" s="184">
         <v>8597.69</v>
       </c>
       <c r="E44" s="115" t="str">
         <f>E42</f>
-        <v>Transf 12/05</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Transf 13/07</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
         <v>3</v>
       </c>
       <c r="B45" s="107"/>
       <c r="C45" s="107"/>
-      <c r="D45" s="170"/>
+      <c r="D45" s="169"/>
       <c r="E45" s="106">
         <f>SUM(D41:D44)</f>
         <v>1268561.71</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B46" s="107"/>
       <c r="C46" s="107"/>
-      <c r="D46" s="168"/>
+      <c r="D46" s="167"/>
       <c r="E46" s="108"/>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="228">
+      <c r="D47" s="184">
         <v>484034.19</v>
       </c>
       <c r="E47" s="113" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="176" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="175" t="s">
         <v>144</v>
       </c>
-      <c r="B48" s="177"/>
+      <c r="B48" s="176"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="228">
+      <c r="D48" s="184">
         <v>17688</v>
       </c>
       <c r="E48" s="113" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="70" t="s">
         <v>107</v>
       </c>
       <c r="B49" s="112"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="228">
+      <c r="D49" s="184">
         <v>1033943.24</v>
       </c>
       <c r="E49" s="113" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
-      <c r="D50" s="171"/>
+      <c r="D50" s="170"/>
       <c r="E50" s="106">
         <f>SUM(D47:D49)</f>
         <v>1535665.43</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="34" t="s">
         <v>143</v>
       </c>
@@ -2492,83 +2530,85 @@
       <c r="D51" s="165"/>
       <c r="E51" s="109"/>
     </row>
-    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="116" t="s">
         <v>57</v>
       </c>
       <c r="B52" s="112"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="228">
+      <c r="D52" s="184">
         <v>189500</v>
       </c>
-      <c r="E52" s="144" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="116" t="s">
-        <v>153</v>
-      </c>
-      <c r="B53" s="112"/>
+      <c r="E52" s="113" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="195" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" s="196"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="169">
-        <v>38400</v>
+      <c r="D53" s="184">
+        <v>110000</v>
       </c>
       <c r="E53" s="144" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="187" t="s">
-        <v>168</v>
-      </c>
-      <c r="B54" s="188"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="195" t="s">
+        <v>161</v>
+      </c>
+      <c r="B54" s="196"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="228">
-        <v>110000</v>
+      <c r="D54" s="184">
+        <v>2493229.87</v>
       </c>
       <c r="E54" s="144" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="187" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="116" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" s="183"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="184">
+        <v>180000</v>
+      </c>
+      <c r="E55" s="144" t="s">
         <v>165</v>
       </c>
-      <c r="B55" s="188"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="228">
-        <v>2493229.87</v>
-      </c>
-      <c r="E55" s="144" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="70" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B56" s="112"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="228">
+      <c r="D56" s="184">
         <v>145000</v>
       </c>
-      <c r="E56" s="144"/>
-    </row>
-    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="113" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="116" t="s">
         <v>133</v>
       </c>
       <c r="B57" s="112"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="228">
+      <c r="D57" s="184">
         <v>60000</v>
       </c>
       <c r="E57" s="144" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
         <v>8</v>
       </c>
@@ -2577,10 +2617,10 @@
       <c r="D58" s="33"/>
       <c r="E58" s="110">
         <f>SUM(D52:D57)</f>
-        <v>3036129.87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>3177729.87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="34" t="s">
         <v>11</v>
       </c>
@@ -2589,29 +2629,29 @@
       <c r="D59" s="163"/>
       <c r="E59" s="109"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="169">
+      <c r="D60" s="168">
         <v>69000</v>
       </c>
       <c r="E60" s="111"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="169">
+      <c r="D61" s="168">
         <v>95455.99</v>
       </c>
       <c r="E61" s="39"/>
     </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="50" t="s">
         <v>15</v>
       </c>
@@ -2623,14 +2663,14 @@
         <v>164455.99</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="67"/>
       <c r="E63" s="75"/>
     </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="30" t="s">
         <v>46</v>
       </c>
@@ -2639,13 +2679,13 @@
       <c r="D64" s="76"/>
       <c r="E64" s="77"/>
     </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="D65" s="78"/>
       <c r="E65" s="79"/>
       <c r="F65" s="42"/>
     </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>12</v>
       </c>
@@ -2654,7 +2694,7 @@
       <c r="D66" s="80"/>
       <c r="E66" s="81">
         <f>(SUM(E28:E64))</f>
-        <v>7700069</v>
+        <v>7841669</v>
       </c>
       <c r="F66" s="101"/>
       <c r="G66" s="42"/>
@@ -2664,7 +2704,7 @@
       <c r="K66" s="89"/>
       <c r="L66" s="89"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D67" s="78"/>
       <c r="E67" s="78"/>
       <c r="H67" s="89"/>
@@ -2673,12 +2713,12 @@
       <c r="K67" s="89"/>
       <c r="L67" s="89"/>
     </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D68" s="78"/>
       <c r="E68" s="78"/>
       <c r="H68" s="118"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>41</v>
       </c>
@@ -2687,35 +2727,35 @@
       <c r="D69" s="82"/>
       <c r="E69" s="83"/>
     </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="187"/>
-      <c r="B70" s="188"/>
+    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="195"/>
+      <c r="B70" s="196"/>
       <c r="C70" s="5"/>
       <c r="D70" s="93"/>
       <c r="E70" s="69"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="187"/>
-      <c r="B71" s="188"/>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="195"/>
+      <c r="B71" s="196"/>
       <c r="C71" s="5"/>
       <c r="D71" s="71"/>
       <c r="E71" s="69"/>
     </row>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="193"/>
-      <c r="B72" s="194"/>
+    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="191"/>
+      <c r="B72" s="192"/>
       <c r="C72" s="5"/>
       <c r="D72" s="71"/>
       <c r="E72" s="69"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="70"/>
       <c r="B73" s="72"/>
       <c r="C73" s="5"/>
       <c r="D73" s="71"/>
       <c r="E73" s="69"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="48"/>
       <c r="B74" s="47"/>
       <c r="C74" s="47"/>
@@ -2725,21 +2765,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="147" t="s">
         <v>19</v>
       </c>
       <c r="B77" s="148"/>
       <c r="C77" s="148"/>
       <c r="D77" s="149"/>
-      <c r="E77" s="178">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E77" s="177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>20</v>
       </c>
@@ -2751,26 +2791,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="65" t="s">
         <v>13</v>
       </c>
       <c r="B81" s="66">
         <f>E66</f>
-        <v>7700069</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7841669</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="65" t="s">
         <v>14</v>
       </c>
       <c r="B82" s="66">
         <f>E66-E64</f>
-        <v>7700069</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>7841669</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="65" t="s">
         <v>21</v>
       </c>
@@ -2779,7 +2819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="65" t="s">
         <v>37</v>
       </c>
@@ -2788,91 +2828,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="195"/>
-      <c r="B87" s="195"/>
-      <c r="C87" s="195"/>
-      <c r="D87" s="195"/>
-      <c r="E87" s="195"/>
-    </row>
-    <row r="88" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="195"/>
-      <c r="B88" s="195"/>
-      <c r="C88" s="195"/>
-      <c r="D88" s="195"/>
-      <c r="E88" s="195"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="195"/>
-      <c r="B89" s="195"/>
-      <c r="C89" s="195"/>
-      <c r="D89" s="195"/>
-      <c r="E89" s="195"/>
-    </row>
-    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="193"/>
+      <c r="B87" s="193"/>
+      <c r="C87" s="193"/>
+      <c r="D87" s="193"/>
+      <c r="E87" s="193"/>
+    </row>
+    <row r="88" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="193"/>
+      <c r="B88" s="193"/>
+      <c r="C88" s="193"/>
+      <c r="D88" s="193"/>
+      <c r="E88" s="193"/>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="193"/>
+      <c r="B89" s="193"/>
+      <c r="C89" s="193"/>
+      <c r="D89" s="193"/>
+      <c r="E89" s="193"/>
+    </row>
+    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="22"/>
       <c r="B91" s="90"/>
       <c r="C91" s="23"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="32"/>
       <c r="B92" s="56">
         <v>0</v>
       </c>
       <c r="C92" s="25"/>
     </row>
-    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="24" t="s">
         <v>7</v>
       </c>
       <c r="B93" s="39">
         <f>PRORRATEO!G34</f>
-        <v>5351853.4400000013</v>
+        <v>4865621.3400000017</v>
       </c>
       <c r="C93" s="23"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="24"/>
       <c r="B94" s="39">
         <v>0</v>
       </c>
       <c r="C94" s="23"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="24" t="s">
         <v>38</v>
       </c>
       <c r="B95" s="73">
         <f>B125</f>
-        <v>0</v>
+        <v>186500</v>
       </c>
       <c r="C95" s="23"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="27"/>
       <c r="B96" s="46"/>
       <c r="C96" s="23"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="88" t="s">
         <v>42</v>
       </c>
       <c r="B97" s="46"/>
       <c r="C97" s="23"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="38" t="s">
         <v>22</v>
       </c>
       <c r="B98" s="46">
         <f>-B82</f>
-        <v>-7700069</v>
+        <v>-7841669</v>
       </c>
       <c r="C98" s="23"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
         <v>23</v>
       </c>
@@ -2882,34 +2922,34 @@
       </c>
       <c r="C99" s="23"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B100" s="56">
         <f>SUM(B92:B99)</f>
-        <v>-2348215.5599999987</v>
+        <v>-2789547.6599999983</v>
       </c>
       <c r="C100" s="26"/>
       <c r="D100" s="42"/>
     </row>
-    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="40"/>
       <c r="C101" s="26"/>
       <c r="D101" s="42"/>
       <c r="E101" s="91"/>
       <c r="F101" s="92"/>
     </row>
-    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="41"/>
       <c r="C102" s="26"/>
     </row>
-    <row r="103" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="B103" s="40"/>
       <c r="C103" s="36"/>
     </row>
-    <row r="104" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="95" t="s">
         <v>126</v>
       </c>
@@ -2920,16 +2960,16 @@
       <c r="D104" s="45"/>
       <c r="E104" s="42"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="52" t="s">
         <v>47</v>
       </c>
       <c r="B105" s="158">
         <f>-B82</f>
-        <v>-7700069</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-7841669</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="52" t="s">
         <v>48</v>
       </c>
@@ -2938,153 +2978,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="B107" s="185">
+        <v>151</v>
+      </c>
+      <c r="B107" s="182">
         <v>163369.25</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="52" t="s">
         <v>51</v>
       </c>
       <c r="B108" s="99">
         <f>B125</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+        <v>186500</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B109" s="100">
         <f>PRORRATEO!G34</f>
-        <v>5351853.4400000013</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4865621.3400000017</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="97" t="s">
         <v>44</v>
       </c>
       <c r="B110" s="98">
         <f>SUM(B104:C109)</f>
-        <v>1945888.3800000018</v>
+        <v>1504556.2800000021</v>
       </c>
       <c r="D110" s="42"/>
       <c r="E110" s="42"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="96"/>
       <c r="B111" s="96"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="96"/>
       <c r="B112" s="96"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="197" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B113" s="197"/>
     </row>
-    <row r="114" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="198"/>
       <c r="B114" s="198"/>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="198"/>
       <c r="B115" s="198"/>
     </row>
-    <row r="116" spans="1:13" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="199"/>
       <c r="B116" s="199"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="96"/>
       <c r="B117" s="96"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="96"/>
       <c r="B118" s="96"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="96"/>
       <c r="B119" s="96"/>
     </row>
-    <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="196" t="s">
+    <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="194" t="s">
         <v>30</v>
       </c>
-      <c r="B121" s="196"/>
-      <c r="C121" s="196"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="196"/>
-      <c r="B122" s="196"/>
-      <c r="C122" s="196"/>
-    </row>
-    <row r="123" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="85"/>
+      <c r="B121" s="194"/>
+      <c r="C121" s="194"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="194"/>
+      <c r="B122" s="194"/>
+      <c r="C122" s="194"/>
+    </row>
+    <row r="123" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="85" t="s">
+        <v>166</v>
+      </c>
       <c r="B123" s="35">
-        <v>0</v>
+        <v>186500</v>
       </c>
       <c r="C123" s="35">
         <v>40000</v>
       </c>
       <c r="E123" s="101"/>
     </row>
-    <row r="124" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="85"/>
       <c r="B124" s="87"/>
       <c r="C124" s="84"/>
       <c r="D124" s="101"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="43" t="s">
         <v>8</v>
       </c>
       <c r="B125" s="86">
         <f>SUM(B123:B124)</f>
-        <v>0</v>
+        <v>186500</v>
       </c>
       <c r="C125" s="44"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M126" s="7"/>
     </row>
-    <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="195"/>
-      <c r="B127" s="195"/>
-      <c r="C127" s="195"/>
-      <c r="D127" s="195"/>
-      <c r="E127" s="195"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A128" s="195"/>
-      <c r="B128" s="195"/>
-      <c r="C128" s="195"/>
-      <c r="D128" s="195"/>
-      <c r="E128" s="195"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="195"/>
-      <c r="B129" s="195"/>
-      <c r="C129" s="195"/>
-      <c r="D129" s="195"/>
-      <c r="E129" s="195"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="195"/>
-      <c r="B130" s="195"/>
-      <c r="C130" s="195"/>
-      <c r="D130" s="195"/>
-      <c r="E130" s="195"/>
+    <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="193"/>
+      <c r="B127" s="193"/>
+      <c r="C127" s="193"/>
+      <c r="D127" s="193"/>
+      <c r="E127" s="193"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="193"/>
+      <c r="B128" s="193"/>
+      <c r="C128" s="193"/>
+      <c r="D128" s="193"/>
+      <c r="E128" s="193"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="193"/>
+      <c r="B129" s="193"/>
+      <c r="C129" s="193"/>
+      <c r="D129" s="193"/>
+      <c r="E129" s="193"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="193"/>
+      <c r="B130" s="193"/>
+      <c r="C130" s="193"/>
+      <c r="D130" s="193"/>
+      <c r="E130" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A127:E130"/>
     <mergeCell ref="A121:C122"/>
@@ -3094,14 +3141,9 @@
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A113:B116"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="110" orientation="portrait" r:id="rId1"/>
@@ -3112,42 +3154,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="207"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3171,7 +3213,7 @@
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3186,7 +3228,7 @@
       <c r="L3" s="57"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="214" t="s">
         <v>138</v>
       </c>
@@ -3203,22 +3245,22 @@
       <c r="L4" s="215"/>
       <c r="M4" s="216"/>
     </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="217"/>
-      <c r="B5" s="186"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
-      <c r="H5" s="186"/>
-      <c r="I5" s="186"/>
-      <c r="J5" s="186"/>
-      <c r="K5" s="186"/>
-      <c r="L5" s="186"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="200"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="200"/>
+      <c r="L5" s="200"/>
       <c r="M5" s="218"/>
     </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="219"/>
       <c r="B6" s="220"/>
       <c r="C6" s="220"/>
@@ -3233,35 +3275,35 @@
       <c r="L6" s="220"/>
       <c r="M6" s="221"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="200" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="200" t="s">
+      <c r="B7" s="209" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="200" t="s">
+      <c r="C7" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="200" t="s">
+      <c r="D7" s="209" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="200" t="s">
+      <c r="E7" s="209" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="208" t="s">
+      <c r="F7" s="207" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="200" t="s">
+      <c r="G7" s="209" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="208" t="s">
+      <c r="I7" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="208" t="s">
+      <c r="J7" s="207" t="s">
         <v>24</v>
       </c>
       <c r="K7" s="212" t="s">
@@ -3270,29 +3312,29 @@
       <c r="L7" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="206" t="s">
+      <c r="M7" s="205" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="200"/>
-      <c r="B8" s="201"/>
-      <c r="C8" s="200"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="200"/>
-      <c r="F8" s="209"/>
-      <c r="G8" s="200"/>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="209"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="222"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="209"/>
       <c r="H8" s="211"/>
-      <c r="I8" s="209"/>
-      <c r="J8" s="209"/>
+      <c r="I8" s="208"/>
+      <c r="J8" s="208"/>
       <c r="K8" s="213"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="M8" s="206"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="205"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="120">
         <v>1</v>
       </c>
@@ -3309,11 +3351,11 @@
         <v>3.43</v>
       </c>
       <c r="F9" s="122">
-        <v>182208.01</v>
-      </c>
-      <c r="G9" s="131">
+        <v>186280.01</v>
+      </c>
+      <c r="G9" s="190">
         <f t="shared" ref="G9:G14" si="0">F9</f>
-        <v>182208.01</v>
+        <v>186280.01</v>
       </c>
       <c r="H9" s="123">
         <f t="shared" ref="H9:H32" si="1">F9-G9</f>
@@ -3343,7 +3385,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="129">
         <f>A9+1</f>
         <v>2</v>
@@ -3363,7 +3405,7 @@
       <c r="F10" s="131">
         <v>160211.01999999999</v>
       </c>
-      <c r="G10" s="131">
+      <c r="G10" s="190">
         <f t="shared" si="0"/>
         <v>160211.01999999999</v>
       </c>
@@ -3397,7 +3439,7 @@
       </c>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="129">
         <f t="shared" ref="A11:A32" si="7">A10+1</f>
         <v>3</v>
@@ -3418,7 +3460,7 @@
       <c r="F11" s="131">
         <v>369301.03</v>
       </c>
-      <c r="G11" s="131">
+      <c r="G11" s="190">
         <f t="shared" si="0"/>
         <v>369301.03</v>
       </c>
@@ -3454,7 +3496,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="120">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3463,22 +3505,21 @@
         <v>63</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D12" s="128"/>
       <c r="E12" s="142">
         <v>3.43</v>
       </c>
       <c r="F12" s="122">
-        <v>182327.04000000001</v>
-      </c>
-      <c r="G12" s="131">
-        <f t="shared" si="0"/>
-        <v>182327.04000000001</v>
+        <v>186280.04</v>
+      </c>
+      <c r="G12" s="190">
+        <v>191868.04</v>
       </c>
       <c r="H12" s="123">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-5588</v>
       </c>
       <c r="I12" s="123">
         <f t="shared" si="4"/>
@@ -3494,11 +3535,11 @@
       </c>
       <c r="L12" s="126">
         <f t="shared" si="2"/>
-        <v>186280.04</v>
+        <v>180692.04</v>
       </c>
       <c r="M12" s="127">
         <f t="shared" si="3"/>
-        <v>191868.04</v>
+        <v>186113.04</v>
       </c>
       <c r="N12" s="42">
         <f t="shared" si="8"/>
@@ -3506,7 +3547,7 @@
       </c>
       <c r="P12" s="42"/>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="120">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3524,8 +3565,8 @@
       <c r="F13" s="122">
         <v>160211.04999999999</v>
       </c>
-      <c r="G13" s="131">
-        <f t="shared" si="0"/>
+      <c r="G13" s="190">
+        <f>F13</f>
         <v>160211.04999999999</v>
       </c>
       <c r="H13" s="123">
@@ -3558,7 +3599,7 @@
       </c>
       <c r="P13" s="42"/>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="129">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3574,11 +3615,11 @@
         <v>5.69</v>
       </c>
       <c r="F14" s="122">
-        <v>302264.06</v>
-      </c>
-      <c r="G14" s="131">
+        <v>309018.06</v>
+      </c>
+      <c r="G14" s="190">
         <f t="shared" si="0"/>
-        <v>302264.06</v>
+        <v>309018.06</v>
       </c>
       <c r="H14" s="123">
         <f t="shared" si="1"/>
@@ -3612,7 +3653,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="120">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3628,18 +3669,16 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="122">
-        <v>326059.07</v>
-      </c>
-      <c r="G15" s="131">
-        <v>279558</v>
-      </c>
+        <v>234176.07</v>
+      </c>
+      <c r="G15" s="131"/>
       <c r="H15" s="123">
         <f t="shared" si="1"/>
-        <v>46501.070000000007</v>
+        <v>234176.07</v>
       </c>
       <c r="I15" s="123">
         <f t="shared" si="4"/>
-        <v>1395.0321000000001</v>
+        <v>7025.2821000000004</v>
       </c>
       <c r="J15" s="124">
         <f t="shared" si="5"/>
@@ -3651,11 +3690,11 @@
       </c>
       <c r="L15" s="126">
         <f t="shared" si="2"/>
-        <v>234176.07</v>
+        <v>427481.07</v>
       </c>
       <c r="M15" s="127">
         <f t="shared" si="3"/>
-        <v>241201.07</v>
+        <v>440305.07</v>
       </c>
       <c r="N15" s="42">
         <f t="shared" si="8"/>
@@ -3665,7 +3704,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="120">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3683,16 +3722,16 @@
         <v>2.95</v>
       </c>
       <c r="F16" s="122">
-        <v>280430.08000000002</v>
+        <v>449054.08</v>
       </c>
       <c r="G16" s="131"/>
       <c r="H16" s="123">
         <f t="shared" si="1"/>
-        <v>280430.08000000002</v>
+        <v>449054.08</v>
       </c>
       <c r="I16" s="123">
         <f t="shared" si="4"/>
-        <v>8412.9024000000009</v>
+        <v>13471.6224</v>
       </c>
       <c r="J16" s="124">
         <f t="shared" si="5"/>
@@ -3704,18 +3743,18 @@
       </c>
       <c r="L16" s="126">
         <f t="shared" si="2"/>
-        <v>449054.08</v>
+        <v>622737.07999999996</v>
       </c>
       <c r="M16" s="127">
         <f t="shared" si="3"/>
-        <v>462526.08</v>
+        <v>641419.07999999996</v>
       </c>
       <c r="N16" s="42">
         <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="120">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3727,17 +3766,17 @@
         <v>117</v>
       </c>
       <c r="D17" s="128" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E17" s="142">
         <v>5.69</v>
       </c>
       <c r="F17" s="122">
-        <v>540897.09</v>
-      </c>
-      <c r="G17" s="131">
+        <v>309018.09000000003</v>
+      </c>
+      <c r="G17" s="190">
         <f>F17</f>
-        <v>540897.09</v>
+        <v>309018.09000000003</v>
       </c>
       <c r="H17" s="123">
         <f t="shared" si="1"/>
@@ -3768,7 +3807,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="120">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3786,14 +3825,14 @@
         <v>3.43</v>
       </c>
       <c r="F18" s="122">
-        <v>186280.1</v>
-      </c>
-      <c r="G18" s="131">
-        <v>191868.1</v>
+        <v>180692.1</v>
+      </c>
+      <c r="G18" s="190">
+        <v>186500</v>
       </c>
       <c r="H18" s="123">
-        <f t="shared" si="1"/>
-        <v>-5588</v>
+        <f>F18-G18</f>
+        <v>-5807.8999999999942</v>
       </c>
       <c r="I18" s="123">
         <f t="shared" si="4"/>
@@ -3809,18 +3848,18 @@
       </c>
       <c r="L18" s="126">
         <f t="shared" si="2"/>
-        <v>180692.1</v>
+        <v>180472.1</v>
       </c>
       <c r="M18" s="127">
         <f t="shared" si="3"/>
-        <v>186113.1</v>
+        <v>185886.1</v>
       </c>
       <c r="N18" s="42">
         <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="120">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3840,7 +3879,7 @@
       <c r="F19" s="122">
         <v>160211.10999999999</v>
       </c>
-      <c r="G19" s="131">
+      <c r="G19" s="190">
         <f>F19</f>
         <v>160211.10999999999</v>
       </c>
@@ -3873,7 +3912,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="120">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3892,14 +3931,14 @@
         <v>6.2</v>
       </c>
       <c r="F20" s="122">
-        <v>336716.12</v>
-      </c>
-      <c r="G20" s="131">
-        <v>346814.12</v>
+        <v>326618.12</v>
+      </c>
+      <c r="G20" s="190">
+        <v>336417.12</v>
       </c>
       <c r="H20" s="123">
         <f t="shared" si="1"/>
-        <v>-10098</v>
+        <v>-9799</v>
       </c>
       <c r="I20" s="123">
         <f t="shared" si="4"/>
@@ -3915,18 +3954,18 @@
       </c>
       <c r="L20" s="126">
         <f t="shared" si="2"/>
-        <v>326618.12</v>
+        <v>326917.12</v>
       </c>
       <c r="M20" s="127">
         <f t="shared" si="3"/>
-        <v>336417.12</v>
+        <v>336725.12</v>
       </c>
       <c r="N20" s="42">
         <f t="shared" si="8"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="120">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3944,11 +3983,11 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="122">
-        <v>180873.13</v>
-      </c>
-      <c r="G21" s="131">
+        <v>186280.13</v>
+      </c>
+      <c r="G21" s="190">
         <f>F21</f>
-        <v>180873.13</v>
+        <v>186280.13</v>
       </c>
       <c r="H21" s="123">
         <f t="shared" si="1"/>
@@ -3979,7 +4018,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="120">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3999,7 +4038,7 @@
       <c r="F22" s="122">
         <v>160211.14000000001</v>
       </c>
-      <c r="G22" s="131">
+      <c r="G22" s="190">
         <f>F22</f>
         <v>160211.14000000001</v>
       </c>
@@ -4032,7 +4071,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="129">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -4053,7 +4092,7 @@
       <c r="F23" s="131">
         <v>336716.15</v>
       </c>
-      <c r="G23" s="133">
+      <c r="G23" s="190">
         <f>F23</f>
         <v>336716.15</v>
       </c>
@@ -4086,7 +4125,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="129">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -4102,14 +4141,14 @@
         <v>3.43</v>
       </c>
       <c r="F24" s="122">
-        <v>186280.16</v>
-      </c>
-      <c r="G24" s="131">
-        <v>191868.16</v>
+        <v>180692.16</v>
+      </c>
+      <c r="G24" s="190">
+        <v>186113.16</v>
       </c>
       <c r="H24" s="123">
         <f t="shared" si="1"/>
-        <v>-5588</v>
+        <v>-5421</v>
       </c>
       <c r="I24" s="123">
         <f t="shared" si="4"/>
@@ -4125,18 +4164,18 @@
       </c>
       <c r="L24" s="126">
         <f t="shared" si="2"/>
-        <v>180692.16</v>
+        <v>180859.16</v>
       </c>
       <c r="M24" s="127">
         <f t="shared" si="3"/>
-        <v>186113.16</v>
+        <v>186285.16</v>
       </c>
       <c r="N24" s="42">
         <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="120">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -4156,7 +4195,7 @@
       <c r="F25" s="131">
         <v>160211.17000000001</v>
       </c>
-      <c r="G25" s="133">
+      <c r="G25" s="190">
         <f>F25</f>
         <v>160211.17000000001</v>
       </c>
@@ -4189,7 +4228,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="129">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4206,11 +4245,11 @@
         <v>6.2</v>
       </c>
       <c r="F26" s="131">
-        <v>344295.18</v>
-      </c>
-      <c r="G26" s="133">
+        <v>336716.18</v>
+      </c>
+      <c r="G26" s="189">
         <f>F26</f>
-        <v>344295.18</v>
+        <v>336716.18</v>
       </c>
       <c r="H26" s="123">
         <f t="shared" si="1"/>
@@ -4241,7 +4280,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="129">
         <f t="shared" si="7"/>
         <v>19</v>
@@ -4259,16 +4298,16 @@
         <v>3.43</v>
       </c>
       <c r="F27" s="131">
-        <v>660257.18999999994</v>
+        <v>866345.19</v>
       </c>
       <c r="G27" s="131"/>
       <c r="H27" s="123">
         <f t="shared" si="1"/>
-        <v>660257.18999999994</v>
+        <v>866345.19</v>
       </c>
       <c r="I27" s="123">
         <f t="shared" si="4"/>
-        <v>19807.715699999997</v>
+        <v>25990.355699999996</v>
       </c>
       <c r="J27" s="124">
         <f t="shared" si="5"/>
@@ -4280,18 +4319,18 @@
       </c>
       <c r="L27" s="126">
         <f t="shared" si="2"/>
-        <v>866345.19</v>
+        <v>1078615.19</v>
       </c>
       <c r="M27" s="127">
         <f t="shared" si="3"/>
-        <v>892335.19</v>
+        <v>1110973.19</v>
       </c>
       <c r="N27" s="42">
         <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="129">
         <f t="shared" si="7"/>
         <v>20</v>
@@ -4311,8 +4350,8 @@
       <c r="F28" s="133">
         <v>160211.20000000001</v>
       </c>
-      <c r="G28" s="131">
-        <f>F28</f>
+      <c r="G28" s="190">
+        <f t="shared" ref="G28" si="9">F28</f>
         <v>160211.20000000001</v>
       </c>
       <c r="H28" s="123">
@@ -4344,7 +4383,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="129">
         <f t="shared" si="7"/>
         <v>21</v>
@@ -4361,14 +4400,14 @@
         <v>6.2</v>
       </c>
       <c r="F29" s="133">
-        <v>329563.21000000002</v>
-      </c>
-      <c r="G29" s="131">
-        <v>339450.21</v>
+        <v>326829.21000000002</v>
+      </c>
+      <c r="G29" s="190">
+        <v>336634.21</v>
       </c>
       <c r="H29" s="123">
         <f t="shared" si="1"/>
-        <v>-9887</v>
+        <v>-9805</v>
       </c>
       <c r="I29" s="123">
         <f t="shared" si="4"/>
@@ -4384,18 +4423,18 @@
       </c>
       <c r="L29" s="126">
         <f t="shared" si="2"/>
-        <v>326829.21000000002</v>
+        <v>326911.21000000002</v>
       </c>
       <c r="M29" s="127">
         <f t="shared" si="3"/>
-        <v>336634.21</v>
+        <v>336718.21</v>
       </c>
       <c r="N29" s="42">
         <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
         <f t="shared" si="7"/>
         <v>22</v>
@@ -4413,18 +4452,18 @@
         <v>3.43</v>
       </c>
       <c r="F30" s="133">
-        <v>320730.21999999997</v>
-      </c>
-      <c r="G30" s="133">
-        <v>140000</v>
+        <v>372432.22</v>
+      </c>
+      <c r="G30" s="189">
+        <v>160000</v>
       </c>
       <c r="H30" s="123">
         <f t="shared" si="1"/>
-        <v>180730.21999999997</v>
+        <v>212432.21999999997</v>
       </c>
       <c r="I30" s="123">
         <f t="shared" si="4"/>
-        <v>5421.9065999999993</v>
+        <v>6372.9665999999988</v>
       </c>
       <c r="J30" s="124">
         <f t="shared" si="5"/>
@@ -4436,18 +4475,18 @@
       </c>
       <c r="L30" s="126">
         <f t="shared" si="2"/>
-        <v>372432.22</v>
+        <v>405085.22</v>
       </c>
       <c r="M30" s="127">
         <f t="shared" si="3"/>
-        <v>383605.22</v>
+        <v>417238.22</v>
       </c>
       <c r="N30" s="42">
         <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="129">
         <f t="shared" si="7"/>
         <v>23</v>
@@ -4465,11 +4504,11 @@
         <v>2.95</v>
       </c>
       <c r="F31" s="133">
-        <v>160211.23000000001</v>
-      </c>
-      <c r="G31" s="133">
+        <v>165017.23000000001</v>
+      </c>
+      <c r="G31" s="189">
         <f>F31</f>
-        <v>160211.23000000001</v>
+        <v>165017.23000000001</v>
       </c>
       <c r="H31" s="123">
         <f t="shared" si="1"/>
@@ -4500,7 +4539,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="120">
         <f t="shared" si="7"/>
         <v>24</v>
@@ -4516,11 +4555,11 @@
         <v>5.68</v>
       </c>
       <c r="F32" s="132">
-        <v>301935.24</v>
-      </c>
-      <c r="G32" s="133">
+        <v>308475.24</v>
+      </c>
+      <c r="G32" s="189">
         <f>F32</f>
-        <v>301935.24</v>
+        <v>308475.24</v>
       </c>
       <c r="H32" s="123">
         <f t="shared" si="1"/>
@@ -4551,9 +4590,9 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="202"/>
-      <c r="B33" s="203"/>
+    <row r="33" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="223"/>
+      <c r="B33" s="224"/>
       <c r="C33" s="135"/>
       <c r="D33" s="135"/>
       <c r="E33" s="121"/>
@@ -4567,132 +4606,140 @@
       <c r="M33" s="127"/>
       <c r="N33" s="42"/>
     </row>
-    <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="204" t="s">
+    <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="225" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="204"/>
-      <c r="C34" s="205"/>
+      <c r="B34" s="225"/>
+      <c r="C34" s="226"/>
       <c r="D34" s="137"/>
       <c r="E34" s="145">
-        <f t="shared" ref="E34:K34" si="9">SUM(E9:E33)</f>
+        <f t="shared" ref="E34:K34" si="10">SUM(E9:E33)</f>
         <v>99.700000000000045</v>
       </c>
       <c r="F34" s="138">
-        <f t="shared" si="9"/>
-        <v>6488611.0000000009</v>
+        <f t="shared" si="10"/>
+        <v>6591208.0000000009</v>
       </c>
       <c r="G34" s="139">
-        <f t="shared" si="9"/>
-        <v>5351853.4400000013</v>
+        <f t="shared" si="10"/>
+        <v>4865621.3400000017</v>
       </c>
       <c r="H34" s="139">
-        <f t="shared" si="9"/>
-        <v>1136757.56</v>
+        <f t="shared" si="10"/>
+        <v>1725586.66</v>
       </c>
       <c r="I34" s="139">
-        <f t="shared" si="9"/>
-        <v>35037.556799999998</v>
+        <f t="shared" si="10"/>
+        <v>52860.226799999997</v>
       </c>
       <c r="J34" s="140">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5414603.1225699997</v>
       </c>
       <c r="K34" s="139">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L34" s="141">
         <f>SUM(L9:L26)</f>
-        <v>4391897.71</v>
+        <v>4753543.71</v>
       </c>
       <c r="M34" s="141">
         <f>SUM(M9:M33)</f>
-        <v>6783991.0000000009</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7408841.0000000009</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="49"/>
       <c r="D35" s="49"/>
     </row>
-    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="195" t="str">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="193" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="195"/>
-      <c r="E37" s="195"/>
-      <c r="F37" s="195"/>
-      <c r="G37" s="195"/>
-      <c r="H37" s="195"/>
-      <c r="I37" s="195"/>
-      <c r="J37" s="195"/>
-      <c r="K37" s="195"/>
-      <c r="L37" s="195"/>
-    </row>
-    <row r="38" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="195"/>
-      <c r="D38" s="195"/>
-      <c r="E38" s="195"/>
-      <c r="F38" s="195"/>
-      <c r="G38" s="195"/>
-      <c r="H38" s="195"/>
-      <c r="I38" s="195"/>
-      <c r="J38" s="195"/>
-      <c r="K38" s="195"/>
-      <c r="L38" s="195"/>
-    </row>
-    <row r="39" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="195"/>
-      <c r="D39" s="195"/>
-      <c r="E39" s="195"/>
-      <c r="F39" s="195"/>
-      <c r="G39" s="195"/>
-      <c r="H39" s="195"/>
-      <c r="I39" s="195"/>
-      <c r="J39" s="195"/>
-      <c r="K39" s="195"/>
-      <c r="L39" s="195"/>
-    </row>
-    <row r="40" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="195"/>
-      <c r="D40" s="195"/>
-      <c r="E40" s="195"/>
-      <c r="F40" s="195"/>
-      <c r="G40" s="195"/>
-      <c r="H40" s="195"/>
-      <c r="I40" s="195"/>
-      <c r="J40" s="195"/>
-      <c r="K40" s="195"/>
-      <c r="L40" s="195"/>
-    </row>
-    <row r="41" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="195"/>
-      <c r="D41" s="195"/>
-      <c r="E41" s="195"/>
-      <c r="F41" s="195"/>
-      <c r="G41" s="195"/>
-      <c r="H41" s="195"/>
-      <c r="I41" s="195"/>
-      <c r="J41" s="195"/>
-      <c r="K41" s="195"/>
-      <c r="L41" s="195"/>
-    </row>
-    <row r="42" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="195"/>
-      <c r="D42" s="195"/>
-      <c r="E42" s="195"/>
-      <c r="F42" s="195"/>
-      <c r="G42" s="195"/>
-      <c r="H42" s="195"/>
-      <c r="I42" s="195"/>
-      <c r="J42" s="195"/>
-      <c r="K42" s="195"/>
-      <c r="L42" s="195"/>
+      <c r="D37" s="193"/>
+      <c r="E37" s="193"/>
+      <c r="F37" s="193"/>
+      <c r="G37" s="193"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="193"/>
+      <c r="K37" s="193"/>
+      <c r="L37" s="193"/>
+    </row>
+    <row r="38" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="193"/>
+      <c r="D38" s="193"/>
+      <c r="E38" s="193"/>
+      <c r="F38" s="193"/>
+      <c r="G38" s="193"/>
+      <c r="H38" s="193"/>
+      <c r="I38" s="193"/>
+      <c r="J38" s="193"/>
+      <c r="K38" s="193"/>
+      <c r="L38" s="193"/>
+    </row>
+    <row r="39" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="193"/>
+      <c r="D39" s="193"/>
+      <c r="E39" s="193"/>
+      <c r="F39" s="193"/>
+      <c r="G39" s="193"/>
+      <c r="H39" s="193"/>
+      <c r="I39" s="193"/>
+      <c r="J39" s="193"/>
+      <c r="K39" s="193"/>
+      <c r="L39" s="193"/>
+    </row>
+    <row r="40" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="193"/>
+      <c r="D40" s="193"/>
+      <c r="E40" s="193"/>
+      <c r="F40" s="193"/>
+      <c r="G40" s="193"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="193"/>
+      <c r="J40" s="193"/>
+      <c r="K40" s="193"/>
+      <c r="L40" s="193"/>
+    </row>
+    <row r="41" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="193"/>
+      <c r="D41" s="193"/>
+      <c r="E41" s="193"/>
+      <c r="F41" s="193"/>
+      <c r="G41" s="193"/>
+      <c r="H41" s="193"/>
+      <c r="I41" s="193"/>
+      <c r="J41" s="193"/>
+      <c r="K41" s="193"/>
+      <c r="L41" s="193"/>
+    </row>
+    <row r="42" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="193"/>
+      <c r="D42" s="193"/>
+      <c r="E42" s="193"/>
+      <c r="F42" s="193"/>
+      <c r="G42" s="193"/>
+      <c r="H42" s="193"/>
+      <c r="I42" s="193"/>
+      <c r="J42" s="193"/>
+      <c r="K42" s="193"/>
+      <c r="L42" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C37:L42"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="I7:I8"/>
@@ -4702,14 +4749,6 @@
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
     <mergeCell ref="A4:M6"/>
-    <mergeCell ref="C37:L42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4719,61 +4758,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="179" t="s">
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="178" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="180"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="173"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="181" t="s">
+      <c r="C3" s="179"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="172"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="180" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="182"/>
-      <c r="G4" s="174"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="175"/>
-      <c r="G5" s="174"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="222"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="224"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="222"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="224"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="222"/>
-      <c r="C8" s="223"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="224"/>
-    </row>
-    <row r="9" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="225"/>
-      <c r="C9" s="226"/>
-      <c r="D9" s="226"/>
-      <c r="E9" s="226"/>
-      <c r="F9" s="226"/>
-      <c r="G9" s="227"/>
+      <c r="C4" s="181"/>
+      <c r="G4" s="173"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="174"/>
+      <c r="G5" s="173"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="227"/>
+      <c r="C6" s="228"/>
+      <c r="D6" s="228"/>
+      <c r="E6" s="228"/>
+      <c r="F6" s="228"/>
+      <c r="G6" s="229"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="227"/>
+      <c r="C7" s="228"/>
+      <c r="D7" s="228"/>
+      <c r="E7" s="228"/>
+      <c r="F7" s="228"/>
+      <c r="G7" s="229"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="227"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="229"/>
+    </row>
+    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="230"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="231"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="231"/>
+      <c r="G9" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2026/ANATOLE FRANCE/Julio/ANATOLE-Julio.xlsx
+++ b/2026/ANATOLE FRANCE/Julio/ANATOLE-Julio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3E7834-0741-4081-B2E2-18F57BD6CDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17242285-DA0F-4439-AE9D-21A1FA9197D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="168">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -486,9 +486,6 @@
     <t>El total del dinero en cuenta corresponde a CAJA EXTRAORDINARIA</t>
   </si>
   <si>
-    <t>Ingreso pago de expensas porteria</t>
-  </si>
-  <si>
     <t>VTO 17/08</t>
   </si>
   <si>
@@ -531,7 +528,13 @@
     <t>Transf 27/07</t>
   </si>
   <si>
-    <t>Deposito sin identificar 13/07</t>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Transf 31/07</t>
+  </si>
+  <si>
+    <t>Suben a $216.000 en juli0</t>
   </si>
 </sst>
 </file>
@@ -549,7 +552,7 @@
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -756,13 +759,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1245,7 +1241,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1500,23 +1496,23 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="27" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2058,11 +2054,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="199" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
       <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2076,12 +2072,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="202" t="s">
+      <c r="B3" s="200" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="202"/>
-      <c r="D3" s="202"/>
-      <c r="E3" s="203"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="201"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -2099,7 +2095,7 @@
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="62" t="s">
@@ -2119,49 +2115,49 @@
       <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="200" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="200"/>
+      <c r="B8" s="198" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="198"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
+      <c r="B10" s="198"/>
+      <c r="C10" s="198"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="204" t="s">
+      <c r="A13" s="202" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="204"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
+      <c r="B13" s="202"/>
+      <c r="C13" s="202"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="204"/>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
+      <c r="A14" s="202"/>
+      <c r="B14" s="202"/>
+      <c r="C14" s="202"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="202"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="204"/>
-      <c r="B15" s="204"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="204"/>
-      <c r="E15" s="204"/>
+      <c r="A15" s="202"/>
+      <c r="B15" s="202"/>
+      <c r="C15" s="202"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="202"/>
     </row>
     <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="204"/>
-      <c r="B16" s="204"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="204"/>
-      <c r="E16" s="204"/>
+      <c r="A16" s="202"/>
+      <c r="B16" s="202"/>
+      <c r="C16" s="202"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="202"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2187,13 +2183,13 @@
       <c r="E21" s="33"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="195" t="s">
+      <c r="A22" s="193" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="196"/>
+      <c r="B22" s="194"/>
       <c r="C22" s="5"/>
       <c r="D22" s="159">
-        <v>1719538.75</v>
+        <v>1338142.06</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -2204,7 +2200,7 @@
       <c r="B23" s="112"/>
       <c r="C23" s="5"/>
       <c r="D23" s="159">
-        <v>-425585.84</v>
+        <v>-331190.06</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -2215,7 +2211,7 @@
       <c r="B24" s="112"/>
       <c r="C24" s="5"/>
       <c r="D24" s="159">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="E24" s="5"/>
     </row>
@@ -2227,7 +2223,7 @@
       <c r="C25" s="54"/>
       <c r="D25" s="160">
         <f>SUM(D22:D24)</f>
-        <v>1293953</v>
+        <v>1006952</v>
       </c>
       <c r="E25" s="102"/>
       <c r="G25" s="21"/>
@@ -2292,7 +2288,7 @@
       <c r="D32" s="163"/>
       <c r="E32" s="103">
         <f>D25+D31</f>
-        <v>1293953</v>
+        <v>1006952</v>
       </c>
       <c r="F32" s="21"/>
     </row>
@@ -2306,29 +2302,32 @@
       <c r="E33" s="104"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="191" t="s">
+      <c r="A34" s="189" t="s">
         <v>132</v>
       </c>
-      <c r="B34" s="192"/>
+      <c r="B34" s="190"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="187">
+      <c r="D34" s="159">
         <v>50000</v>
       </c>
       <c r="E34" s="113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="191" t="s">
-        <v>155</v>
-      </c>
-      <c r="B35" s="192"/>
+      <c r="A35" s="189" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="190"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="185">
+      <c r="D35" s="186">
         <v>190000</v>
       </c>
       <c r="E35" s="113" t="s">
-        <v>162</v>
+        <v>161</v>
+      </c>
+      <c r="G35" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2353,12 +2352,12 @@
       <c r="E37" s="105"/>
     </row>
     <row r="38" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="195" t="s">
+      <c r="A38" s="193" t="s">
         <v>142</v>
       </c>
-      <c r="B38" s="196"/>
+      <c r="B38" s="194"/>
       <c r="C38" s="52"/>
-      <c r="D38" s="188">
+      <c r="D38" s="187">
         <v>161303</v>
       </c>
       <c r="E38" s="119" t="s">
@@ -2392,27 +2391,27 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="51"/>
-      <c r="D41" s="186">
+      <c r="D41" s="188">
         <v>1034496.5</v>
       </c>
       <c r="E41" s="113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G41" s="89"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="184">
+      <c r="D42" s="168">
         <v>77379.5</v>
       </c>
       <c r="E42" s="113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2424,7 +2423,7 @@
         <v>110</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="184">
+      <c r="D43" s="168">
         <v>148088.01999999999</v>
       </c>
       <c r="E43" s="114" t="str">
@@ -2441,7 +2440,7 @@
         <v>109</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="184">
+      <c r="D44" s="168">
         <v>8597.69</v>
       </c>
       <c r="E44" s="115" t="str">
@@ -2476,11 +2475,11 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="184">
+      <c r="D47" s="168">
         <v>484034.19</v>
       </c>
       <c r="E47" s="113" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2489,11 +2488,11 @@
       </c>
       <c r="B48" s="176"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="184">
+      <c r="D48" s="168">
         <v>17688</v>
       </c>
       <c r="E48" s="113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2502,11 +2501,11 @@
       </c>
       <c r="B49" s="112"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="184">
+      <c r="D49" s="168">
         <v>1033943.24</v>
       </c>
       <c r="E49" s="113" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2536,454 +2535,460 @@
       </c>
       <c r="B52" s="112"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="184">
+      <c r="D52" s="168">
         <v>189500</v>
       </c>
       <c r="E52" s="113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="195" t="s">
+      <c r="A53" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" s="194"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="168">
+        <v>110000</v>
+      </c>
+      <c r="E53" s="144" t="s">
         <v>159</v>
       </c>
-      <c r="B53" s="196"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="184">
-        <v>110000</v>
-      </c>
-      <c r="E53" s="144" t="s">
+    </row>
+    <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="193" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="195" t="s">
-        <v>161</v>
-      </c>
-      <c r="B54" s="196"/>
+      <c r="B54" s="194"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="184">
+      <c r="D54" s="168">
         <v>2493229.87</v>
       </c>
       <c r="E54" s="144" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="116" t="s">
+        <v>163</v>
+      </c>
+      <c r="B55" s="182"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="168">
+        <v>180000</v>
+      </c>
+      <c r="E55" s="144" t="s">
         <v>164</v>
-      </c>
-      <c r="B55" s="183"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="184">
-        <v>180000</v>
-      </c>
-      <c r="E55" s="144" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="70" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B56" s="112"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="184">
+      <c r="D56" s="168">
         <v>145000</v>
       </c>
       <c r="E56" s="113" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="116" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="183" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" s="184"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="168">
+        <v>226800</v>
+      </c>
+      <c r="E57" s="185" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="116" t="s">
         <v>133</v>
       </c>
-      <c r="B57" s="112"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="184">
+      <c r="B58" s="112"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="168">
         <v>60000</v>
       </c>
-      <c r="E57" s="144" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="29" t="s">
+      <c r="E58" s="144" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="110">
-        <f>SUM(D52:D57)</f>
-        <v>3177729.87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="34" t="s">
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="110">
+        <f>SUM(D52:D58)</f>
+        <v>3404529.87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="59"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="163"/>
-      <c r="E59" s="109"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="168">
-        <v>69000</v>
-      </c>
-      <c r="E60" s="111"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="163"/>
+      <c r="E60" s="109"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="168">
-        <v>95455.99</v>
-      </c>
-      <c r="E61" s="39"/>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="50" t="s">
+        <v>69000</v>
+      </c>
+      <c r="E61" s="111"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="168">
+        <f>-319+104614.71</f>
+        <v>104295.71</v>
+      </c>
+      <c r="E62" s="39"/>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B62" s="50"/>
-      <c r="C62" s="50"/>
-      <c r="D62" s="74"/>
-      <c r="E62" s="68">
-        <f>SUM(D60:D61)</f>
-        <v>164455.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="75"/>
+      <c r="B63" s="50"/>
+      <c r="C63" s="50"/>
+      <c r="D63" s="74"/>
+      <c r="E63" s="68">
+        <f>SUM(D61:D62)</f>
+        <v>173295.71000000002</v>
+      </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="75"/>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="76"/>
-      <c r="E64" s="77"/>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="D65" s="78"/>
-      <c r="E65" s="79"/>
-      <c r="F65" s="42"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="76"/>
+      <c r="E65" s="77"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="1"/>
+      <c r="D66" s="78"/>
+      <c r="E66" s="79"/>
+      <c r="F66" s="42"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="81">
-        <f>(SUM(E28:E64))</f>
-        <v>7841669</v>
-      </c>
-      <c r="F66" s="101"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="89"/>
-      <c r="I66" s="89"/>
-      <c r="J66" s="89"/>
-      <c r="K66" s="89"/>
-      <c r="L66" s="89"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D67" s="78"/>
-      <c r="E67" s="78"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="80"/>
+      <c r="E67" s="81">
+        <f>(SUM(E28:E65))</f>
+        <v>7790307.7199999997</v>
+      </c>
+      <c r="F67" s="101"/>
+      <c r="G67" s="42"/>
       <c r="H67" s="89"/>
       <c r="I67" s="89"/>
       <c r="J67" s="89"/>
       <c r="K67" s="89"/>
       <c r="L67" s="89"/>
     </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D68" s="78"/>
       <c r="E68" s="78"/>
-      <c r="H68" s="118"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="10" t="s">
+      <c r="H68" s="89"/>
+      <c r="I68" s="89"/>
+      <c r="J68" s="89"/>
+      <c r="K68" s="89"/>
+      <c r="L68" s="89"/>
+    </row>
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="H69" s="118"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="83"/>
-    </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="195"/>
-      <c r="B70" s="196"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="93"/>
-      <c r="E70" s="69"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="195"/>
-      <c r="B71" s="196"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="83"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="193"/>
+      <c r="B71" s="194"/>
       <c r="C71" s="5"/>
-      <c r="D71" s="71"/>
+      <c r="D71" s="93"/>
       <c r="E71" s="69"/>
     </row>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="191"/>
-      <c r="B72" s="192"/>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="193"/>
+      <c r="B72" s="194"/>
       <c r="C72" s="5"/>
       <c r="D72" s="71"/>
       <c r="E72" s="69"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="70"/>
-      <c r="B73" s="72"/>
+    <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="189"/>
+      <c r="B73" s="190"/>
       <c r="C73" s="5"/>
       <c r="D73" s="71"/>
       <c r="E73" s="69"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="48"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="55"/>
-      <c r="E74" s="55">
-        <f>SUM(D70:D73)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="147" t="s">
+      <c r="A74" s="70"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="71"/>
+      <c r="E74" s="69"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="48"/>
+      <c r="B75" s="47"/>
+      <c r="C75" s="47"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="55">
+        <f>SUM(D71:D74)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="B77" s="148"/>
-      <c r="C77" s="148"/>
-      <c r="D77" s="149"/>
-      <c r="E77" s="177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="B78" s="148"/>
+      <c r="C78" s="148"/>
+      <c r="D78" s="149"/>
+      <c r="E78" s="177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="60">
-        <f>E74+E77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="B81" s="66">
-        <f>E66</f>
-        <v>7841669</v>
-      </c>
-    </row>
+      <c r="B80" s="9"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="60">
+        <f>E75+E78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B82" s="66">
-        <f>E66-E64</f>
-        <v>7841669</v>
+        <f>E67</f>
+        <v>7790307.7199999997</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="65" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B83" s="66">
-        <f>E79-E77</f>
-        <v>0</v>
+        <f>E67-E65</f>
+        <v>7790307.7199999997</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="66">
+        <f>E80-E78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B84" s="66">
-        <f>E79</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="193"/>
-      <c r="B87" s="193"/>
-      <c r="C87" s="193"/>
-      <c r="D87" s="193"/>
-      <c r="E87" s="193"/>
-    </row>
-    <row r="88" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="193"/>
-      <c r="B88" s="193"/>
-      <c r="C88" s="193"/>
-      <c r="D88" s="193"/>
-      <c r="E88" s="193"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="193"/>
-      <c r="B89" s="193"/>
-      <c r="C89" s="193"/>
-      <c r="D89" s="193"/>
-      <c r="E89" s="193"/>
-    </row>
-    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="22"/>
-      <c r="B91" s="90"/>
-      <c r="C91" s="23"/>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="32"/>
-      <c r="B92" s="56">
-        <v>0</v>
-      </c>
-      <c r="C92" s="25"/>
-    </row>
-    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="24" t="s">
+      <c r="B85" s="66">
+        <f>E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="191"/>
+      <c r="B88" s="191"/>
+      <c r="C88" s="191"/>
+      <c r="D88" s="191"/>
+      <c r="E88" s="191"/>
+    </row>
+    <row r="89" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="191"/>
+      <c r="B89" s="191"/>
+      <c r="C89" s="191"/>
+      <c r="D89" s="191"/>
+      <c r="E89" s="191"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="191"/>
+      <c r="B90" s="191"/>
+      <c r="C90" s="191"/>
+      <c r="D90" s="191"/>
+      <c r="E90" s="191"/>
+    </row>
+    <row r="92" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="22"/>
+      <c r="B92" s="90"/>
+      <c r="C92" s="23"/>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="32"/>
+      <c r="B93" s="56">
+        <v>0</v>
+      </c>
+      <c r="C93" s="25"/>
+    </row>
+    <row r="94" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B93" s="39">
+      <c r="B94" s="39">
         <f>PRORRATEO!G34</f>
-        <v>4865621.3400000017</v>
-      </c>
-      <c r="C93" s="23"/>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="24"/>
-      <c r="B94" s="39">
-        <v>0</v>
+        <v>5106822.3400000017</v>
       </c>
       <c r="C94" s="23"/>
     </row>
     <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="24" t="s">
+      <c r="A95" s="24"/>
+      <c r="B95" s="39">
+        <v>0</v>
+      </c>
+      <c r="C95" s="23"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B95" s="73">
+      <c r="B96" s="73">
         <f>B125</f>
-        <v>186500</v>
-      </c>
-      <c r="C95" s="23"/>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="27"/>
-      <c r="B96" s="46"/>
+        <v>0</v>
+      </c>
       <c r="C96" s="23"/>
     </row>
     <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="88" t="s">
-        <v>42</v>
-      </c>
+      <c r="A97" s="27"/>
       <c r="B97" s="46"/>
       <c r="C97" s="23"/>
     </row>
     <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="38" t="s">
+      <c r="A98" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B98" s="46"/>
+      <c r="C98" s="23"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B98" s="46">
-        <f>-B82</f>
-        <v>-7841669</v>
-      </c>
-      <c r="C98" s="23"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="27" t="s">
+      <c r="B99" s="46">
+        <f>-B83</f>
+        <v>-7790307.7199999997</v>
+      </c>
+      <c r="C99" s="23"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B99" s="46">
-        <f>-(B83)</f>
-        <v>0</v>
-      </c>
-      <c r="C99" s="23"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="31" t="s">
+      <c r="B100" s="46">
+        <f>-(B84)</f>
+        <v>0</v>
+      </c>
+      <c r="C100" s="23"/>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B100" s="56">
-        <f>SUM(B92:B99)</f>
-        <v>-2789547.6599999983</v>
-      </c>
-      <c r="C100" s="26"/>
-      <c r="D100" s="42"/>
-    </row>
-    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="40"/>
+      <c r="B101" s="56">
+        <f>SUM(B93:B100)</f>
+        <v>-2683485.379999998</v>
+      </c>
       <c r="C101" s="26"/>
       <c r="D101" s="42"/>
-      <c r="E101" s="91"/>
-      <c r="F101" s="92"/>
-    </row>
-    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="41"/>
+    </row>
+    <row r="102" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="40"/>
       <c r="C102" s="26"/>
-    </row>
-    <row r="103" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-      <c r="B103" s="40"/>
-      <c r="C103" s="36"/>
-    </row>
-    <row r="104" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="95" t="s">
+      <c r="D102" s="42"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="92"/>
+    </row>
+    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="41"/>
+      <c r="C103" s="26"/>
+    </row>
+    <row r="104" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104"/>
+      <c r="B104" s="40"/>
+      <c r="C104" s="36"/>
+    </row>
+    <row r="105" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="95" t="s">
         <v>126</v>
       </c>
-      <c r="B104" s="146">
-        <v>4130734.6900000004</v>
-      </c>
-      <c r="C104" s="36"/>
-      <c r="D104" s="45"/>
-      <c r="E104" s="42"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B105" s="158">
-        <f>-B82</f>
-        <v>-7841669</v>
-      </c>
+      <c r="B105" s="146">
+        <v>3557534.8000000017</v>
+      </c>
+      <c r="C105" s="36"/>
+      <c r="D105" s="45"/>
+      <c r="E105" s="42"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B106" s="99">
+        <v>47</v>
+      </c>
+      <c r="B106" s="158">
         <f>-B83</f>
-        <v>0</v>
+        <v>-7790307.7199999997</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="52" t="s">
-        <v>151</v>
-      </c>
-      <c r="B107" s="182">
-        <v>163369.25</v>
+        <v>48</v>
+      </c>
+      <c r="B107" s="99">
+        <f>-B84</f>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -2992,7 +2997,7 @@
       </c>
       <c r="B108" s="99">
         <f>B125</f>
-        <v>186500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,7 +3006,7 @@
       </c>
       <c r="B109" s="100">
         <f>PRORRATEO!G34</f>
-        <v>4865621.3400000017</v>
+        <v>5106822.3400000017</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3009,8 +3014,8 @@
         <v>44</v>
       </c>
       <c r="B110" s="98">
-        <f>SUM(B104:C109)</f>
-        <v>1504556.2800000021</v>
+        <f>SUM(B105:C109)</f>
+        <v>874049.42000000365</v>
       </c>
       <c r="D110" s="42"/>
       <c r="E110" s="42"/>
@@ -3024,22 +3029,22 @@
       <c r="B112" s="96"/>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="197" t="s">
+      <c r="A113" s="195" t="s">
         <v>150</v>
       </c>
-      <c r="B113" s="197"/>
+      <c r="B113" s="195"/>
     </row>
     <row r="114" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="198"/>
-      <c r="B114" s="198"/>
+      <c r="A114" s="196"/>
+      <c r="B114" s="196"/>
     </row>
     <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="198"/>
-      <c r="B115" s="198"/>
+      <c r="A115" s="196"/>
+      <c r="B115" s="196"/>
     </row>
     <row r="116" spans="1:13" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="199"/>
-      <c r="B116" s="199"/>
+      <c r="A116" s="197"/>
+      <c r="B116" s="197"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="96"/>
@@ -3055,24 +3060,20 @@
     </row>
     <row r="120" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="194" t="s">
+      <c r="A121" s="192" t="s">
         <v>30</v>
       </c>
-      <c r="B121" s="194"/>
-      <c r="C121" s="194"/>
+      <c r="B121" s="192"/>
+      <c r="C121" s="192"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="194"/>
-      <c r="B122" s="194"/>
-      <c r="C122" s="194"/>
+      <c r="A122" s="192"/>
+      <c r="B122" s="192"/>
+      <c r="C122" s="192"/>
     </row>
     <row r="123" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="85" t="s">
-        <v>166</v>
-      </c>
-      <c r="B123" s="35">
-        <v>186500</v>
-      </c>
+      <c r="A123" s="85"/>
+      <c r="B123" s="35"/>
       <c r="C123" s="35">
         <v>40000</v>
       </c>
@@ -3090,7 +3091,7 @@
       </c>
       <c r="B125" s="86">
         <f>SUM(B123:B124)</f>
-        <v>186500</v>
+        <v>0</v>
       </c>
       <c r="C125" s="44"/>
     </row>
@@ -3098,32 +3099,32 @@
       <c r="M126" s="7"/>
     </row>
     <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="193"/>
-      <c r="B127" s="193"/>
-      <c r="C127" s="193"/>
-      <c r="D127" s="193"/>
-      <c r="E127" s="193"/>
+      <c r="A127" s="191"/>
+      <c r="B127" s="191"/>
+      <c r="C127" s="191"/>
+      <c r="D127" s="191"/>
+      <c r="E127" s="191"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="193"/>
-      <c r="B128" s="193"/>
-      <c r="C128" s="193"/>
-      <c r="D128" s="193"/>
-      <c r="E128" s="193"/>
+      <c r="A128" s="191"/>
+      <c r="B128" s="191"/>
+      <c r="C128" s="191"/>
+      <c r="D128" s="191"/>
+      <c r="E128" s="191"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="193"/>
-      <c r="B129" s="193"/>
-      <c r="C129" s="193"/>
-      <c r="D129" s="193"/>
-      <c r="E129" s="193"/>
+      <c r="A129" s="191"/>
+      <c r="B129" s="191"/>
+      <c r="C129" s="191"/>
+      <c r="D129" s="191"/>
+      <c r="E129" s="191"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="193"/>
-      <c r="B130" s="193"/>
-      <c r="C130" s="193"/>
-      <c r="D130" s="193"/>
-      <c r="E130" s="193"/>
+      <c r="A130" s="191"/>
+      <c r="B130" s="191"/>
+      <c r="C130" s="191"/>
+      <c r="D130" s="191"/>
+      <c r="E130" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -3135,10 +3136,10 @@
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A127:E130"/>
     <mergeCell ref="A121:C122"/>
-    <mergeCell ref="A87:E89"/>
+    <mergeCell ref="A88:E90"/>
+    <mergeCell ref="A72:B72"/>
     <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A53:B53"/>
@@ -3179,14 +3180,14 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
       <c r="M1" s="6"/>
     </row>
     <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3207,7 +3208,8 @@
         <v>50</v>
       </c>
       <c r="K2" s="150">
-        <v>5430895.8100000005</v>
+        <f>5430895.81+5430895.81*10%</f>
+        <v>5973985.3909999998</v>
       </c>
       <c r="L2" s="94"/>
       <c r="M2" s="53"/>
@@ -3229,110 +3231,110 @@
       <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="214" t="s">
+      <c r="A4" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="215"/>
-      <c r="C4" s="215"/>
-      <c r="D4" s="215"/>
-      <c r="E4" s="215"/>
-      <c r="F4" s="215"/>
-      <c r="G4" s="215"/>
-      <c r="H4" s="215"/>
-      <c r="I4" s="215"/>
-      <c r="J4" s="215"/>
-      <c r="K4" s="215"/>
-      <c r="L4" s="215"/>
-      <c r="M4" s="216"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="214"/>
     </row>
     <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="217"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="200"/>
-      <c r="F5" s="200"/>
-      <c r="G5" s="200"/>
-      <c r="H5" s="200"/>
-      <c r="I5" s="200"/>
-      <c r="J5" s="200"/>
-      <c r="K5" s="200"/>
-      <c r="L5" s="200"/>
-      <c r="M5" s="218"/>
+      <c r="A5" s="215"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+      <c r="G5" s="198"/>
+      <c r="H5" s="198"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="198"/>
+      <c r="K5" s="198"/>
+      <c r="L5" s="198"/>
+      <c r="M5" s="216"/>
     </row>
     <row r="6" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="219"/>
-      <c r="B6" s="220"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
-      <c r="F6" s="220"/>
-      <c r="G6" s="220"/>
-      <c r="H6" s="220"/>
-      <c r="I6" s="220"/>
-      <c r="J6" s="220"/>
-      <c r="K6" s="220"/>
-      <c r="L6" s="220"/>
-      <c r="M6" s="221"/>
+      <c r="A6" s="217"/>
+      <c r="B6" s="218"/>
+      <c r="C6" s="218"/>
+      <c r="D6" s="218"/>
+      <c r="E6" s="218"/>
+      <c r="F6" s="218"/>
+      <c r="G6" s="218"/>
+      <c r="H6" s="218"/>
+      <c r="I6" s="218"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="218"/>
+      <c r="L6" s="218"/>
+      <c r="M6" s="219"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="209" t="s">
+      <c r="A7" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="209" t="s">
+      <c r="B7" s="207" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="209" t="s">
+      <c r="C7" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="209" t="s">
+      <c r="D7" s="207" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="209" t="s">
+      <c r="E7" s="207" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="207" t="s">
+      <c r="F7" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="209" t="s">
+      <c r="G7" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="210" t="s">
+      <c r="H7" s="208" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="207" t="s">
+      <c r="I7" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="207" t="s">
+      <c r="J7" s="205" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="212" t="s">
+      <c r="K7" s="210" t="s">
         <v>59</v>
       </c>
       <c r="L7" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="205" t="s">
+      <c r="M7" s="203" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="209"/>
-      <c r="B8" s="222"/>
-      <c r="C8" s="209"/>
-      <c r="D8" s="222"/>
-      <c r="E8" s="209"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="209"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="208"/>
-      <c r="J8" s="208"/>
-      <c r="K8" s="213"/>
+      <c r="A8" s="207"/>
+      <c r="B8" s="220"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="220"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="206"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="209"/>
+      <c r="I8" s="206"/>
+      <c r="J8" s="206"/>
+      <c r="K8" s="211"/>
       <c r="L8" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="M8" s="205"/>
+      <c r="M8" s="203"/>
     </row>
     <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="120">
@@ -3353,7 +3355,7 @@
       <c r="F9" s="122">
         <v>186280.01</v>
       </c>
-      <c r="G9" s="190">
+      <c r="G9" s="131">
         <f t="shared" ref="G9:G14" si="0">F9</f>
         <v>186280.01</v>
       </c>
@@ -3367,7 +3369,7 @@
       </c>
       <c r="J9" s="124">
         <f>K$2*E9%</f>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K9" s="125">
         <f>G$2*E9/100</f>
@@ -3375,11 +3377,11 @@
       </c>
       <c r="L9" s="126">
         <f t="shared" ref="L9:L32" si="2">ROUND(SUM(H9:K9),0) + N9</f>
-        <v>186280.01</v>
+        <v>204908.01</v>
       </c>
       <c r="M9" s="127">
         <f t="shared" ref="M9:M32" si="3">ROUND(L9*3%,0) + L9</f>
-        <v>191868.01</v>
+        <v>211055.01</v>
       </c>
       <c r="N9" s="42">
         <v>0.01</v>
@@ -3405,7 +3407,7 @@
       <c r="F10" s="131">
         <v>160211.01999999999</v>
       </c>
-      <c r="G10" s="190">
+      <c r="G10" s="131">
         <f t="shared" si="0"/>
         <v>160211.01999999999</v>
       </c>
@@ -3419,7 +3421,7 @@
       </c>
       <c r="J10" s="124">
         <f t="shared" ref="J10:J32" si="5">K$2*E10%</f>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ref="K10:K32" si="6">G$2*E10/100</f>
@@ -3427,11 +3429,11 @@
       </c>
       <c r="L10" s="126">
         <f t="shared" si="2"/>
-        <v>160211.01999999999</v>
+        <v>176233.02</v>
       </c>
       <c r="M10" s="127">
         <f t="shared" si="3"/>
-        <v>165017.01999999999</v>
+        <v>181520.02</v>
       </c>
       <c r="N10" s="42">
         <f>N9+0.01</f>
@@ -3460,7 +3462,7 @@
       <c r="F11" s="131">
         <v>369301.03</v>
       </c>
-      <c r="G11" s="190">
+      <c r="G11" s="131">
         <f t="shared" si="0"/>
         <v>369301.03</v>
       </c>
@@ -3474,7 +3476,7 @@
       </c>
       <c r="J11" s="124">
         <f t="shared" si="5"/>
-        <v>369300.91508000006</v>
+        <v>406231.00658799999</v>
       </c>
       <c r="K11" s="125">
         <f t="shared" si="6"/>
@@ -3482,11 +3484,11 @@
       </c>
       <c r="L11" s="126">
         <f t="shared" si="2"/>
-        <v>369301.03</v>
+        <v>406231.03</v>
       </c>
       <c r="M11" s="127">
         <f t="shared" si="3"/>
-        <v>380380.03</v>
+        <v>418418.03</v>
       </c>
       <c r="N11" s="42">
         <f t="shared" ref="N11:N32" si="8">N10+0.01</f>
@@ -3514,7 +3516,7 @@
       <c r="F12" s="122">
         <v>186280.04</v>
       </c>
-      <c r="G12" s="190">
+      <c r="G12" s="131">
         <v>191868.04</v>
       </c>
       <c r="H12" s="123">
@@ -3527,7 +3529,7 @@
       </c>
       <c r="J12" s="124">
         <f t="shared" si="5"/>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K12" s="125">
         <f t="shared" si="6"/>
@@ -3535,11 +3537,11 @@
       </c>
       <c r="L12" s="126">
         <f t="shared" si="2"/>
-        <v>180692.04</v>
+        <v>199320.04</v>
       </c>
       <c r="M12" s="127">
         <f t="shared" si="3"/>
-        <v>186113.04</v>
+        <v>205300.04</v>
       </c>
       <c r="N12" s="42">
         <f t="shared" si="8"/>
@@ -3565,7 +3567,7 @@
       <c r="F13" s="122">
         <v>160211.04999999999</v>
       </c>
-      <c r="G13" s="190">
+      <c r="G13" s="131">
         <f>F13</f>
         <v>160211.04999999999</v>
       </c>
@@ -3579,7 +3581,7 @@
       </c>
       <c r="J13" s="124">
         <f t="shared" si="5"/>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K13" s="125">
         <f t="shared" si="6"/>
@@ -3587,11 +3589,11 @@
       </c>
       <c r="L13" s="126">
         <f t="shared" si="2"/>
-        <v>160211.04999999999</v>
+        <v>176233.05</v>
       </c>
       <c r="M13" s="127">
         <f t="shared" si="3"/>
-        <v>165017.04999999999</v>
+        <v>181520.05</v>
       </c>
       <c r="N13" s="42">
         <f t="shared" si="8"/>
@@ -3617,7 +3619,7 @@
       <c r="F14" s="122">
         <v>309018.06</v>
       </c>
-      <c r="G14" s="190">
+      <c r="G14" s="131">
         <f t="shared" si="0"/>
         <v>309018.06</v>
       </c>
@@ -3631,7 +3633,7 @@
       </c>
       <c r="J14" s="124">
         <f t="shared" si="5"/>
-        <v>309017.97158900008</v>
+        <v>339919.76874790003</v>
       </c>
       <c r="K14" s="125">
         <f t="shared" si="6"/>
@@ -3639,11 +3641,11 @@
       </c>
       <c r="L14" s="126">
         <f t="shared" si="2"/>
-        <v>309018.06</v>
+        <v>339920.06</v>
       </c>
       <c r="M14" s="127">
         <f t="shared" si="3"/>
-        <v>318289.06</v>
+        <v>350118.06</v>
       </c>
       <c r="N14" s="42">
         <f t="shared" si="8"/>
@@ -3669,20 +3671,23 @@
         <v>3.43</v>
       </c>
       <c r="F15" s="122">
-        <v>234176.07</v>
-      </c>
-      <c r="G15" s="131"/>
+        <v>241201</v>
+      </c>
+      <c r="G15" s="131">
+        <f>F15</f>
+        <v>241201</v>
+      </c>
       <c r="H15" s="123">
         <f t="shared" si="1"/>
-        <v>234176.07</v>
+        <v>0</v>
       </c>
       <c r="I15" s="123">
         <f t="shared" si="4"/>
-        <v>7025.2821000000004</v>
+        <v>0</v>
       </c>
       <c r="J15" s="124">
         <f t="shared" si="5"/>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K15" s="125">
         <f t="shared" si="6"/>
@@ -3690,11 +3695,11 @@
       </c>
       <c r="L15" s="126">
         <f t="shared" si="2"/>
-        <v>427481.07</v>
+        <v>204908.07</v>
       </c>
       <c r="M15" s="127">
         <f t="shared" si="3"/>
-        <v>440305.07</v>
+        <v>211055.07</v>
       </c>
       <c r="N15" s="42">
         <f t="shared" si="8"/>
@@ -3735,7 +3740,7 @@
       </c>
       <c r="J16" s="124">
         <f t="shared" si="5"/>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K16" s="125">
         <f t="shared" si="6"/>
@@ -3743,11 +3748,11 @@
       </c>
       <c r="L16" s="126">
         <f t="shared" si="2"/>
-        <v>622737.07999999996</v>
+        <v>638758.07999999996</v>
       </c>
       <c r="M16" s="127">
         <f t="shared" si="3"/>
-        <v>641419.07999999996</v>
+        <v>657921.07999999996</v>
       </c>
       <c r="N16" s="42">
         <f t="shared" si="8"/>
@@ -3774,7 +3779,7 @@
       <c r="F17" s="122">
         <v>309018.09000000003</v>
       </c>
-      <c r="G17" s="190">
+      <c r="G17" s="131">
         <f>F17</f>
         <v>309018.09000000003</v>
       </c>
@@ -3788,7 +3793,7 @@
       </c>
       <c r="J17" s="124">
         <f t="shared" si="5"/>
-        <v>309017.97158900008</v>
+        <v>339919.76874790003</v>
       </c>
       <c r="K17" s="125">
         <f t="shared" si="6"/>
@@ -3796,11 +3801,11 @@
       </c>
       <c r="L17" s="126">
         <f t="shared" si="2"/>
-        <v>309018.09000000003</v>
+        <v>339920.09</v>
       </c>
       <c r="M17" s="127">
         <f t="shared" si="3"/>
-        <v>318289.09000000003</v>
+        <v>350118.09</v>
       </c>
       <c r="N17" s="42">
         <f t="shared" si="8"/>
@@ -3827,7 +3832,7 @@
       <c r="F18" s="122">
         <v>180692.1</v>
       </c>
-      <c r="G18" s="190">
+      <c r="G18" s="131">
         <v>186500</v>
       </c>
       <c r="H18" s="123">
@@ -3840,7 +3845,7 @@
       </c>
       <c r="J18" s="124">
         <f t="shared" si="5"/>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K18" s="125">
         <f t="shared" si="6"/>
@@ -3848,11 +3853,11 @@
       </c>
       <c r="L18" s="126">
         <f t="shared" si="2"/>
-        <v>180472.1</v>
+        <v>199100.1</v>
       </c>
       <c r="M18" s="127">
         <f t="shared" si="3"/>
-        <v>185886.1</v>
+        <v>205073.1</v>
       </c>
       <c r="N18" s="42">
         <f t="shared" si="8"/>
@@ -3879,7 +3884,7 @@
       <c r="F19" s="122">
         <v>160211.10999999999</v>
       </c>
-      <c r="G19" s="190">
+      <c r="G19" s="131">
         <f>F19</f>
         <v>160211.10999999999</v>
       </c>
@@ -3893,7 +3898,7 @@
       </c>
       <c r="J19" s="124">
         <f t="shared" si="5"/>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K19" s="125">
         <f t="shared" si="6"/>
@@ -3901,11 +3906,11 @@
       </c>
       <c r="L19" s="126">
         <f t="shared" si="2"/>
-        <v>160211.10999999999</v>
+        <v>176233.11</v>
       </c>
       <c r="M19" s="127">
         <f t="shared" si="3"/>
-        <v>165017.10999999999</v>
+        <v>181520.11</v>
       </c>
       <c r="N19" s="42">
         <f t="shared" si="8"/>
@@ -3933,7 +3938,7 @@
       <c r="F20" s="122">
         <v>326618.12</v>
       </c>
-      <c r="G20" s="190">
+      <c r="G20" s="131">
         <v>336417.12</v>
       </c>
       <c r="H20" s="123">
@@ -3946,7 +3951,7 @@
       </c>
       <c r="J20" s="124">
         <f t="shared" si="5"/>
-        <v>336715.54022000002</v>
+        <v>370387.09424199996</v>
       </c>
       <c r="K20" s="125">
         <f t="shared" si="6"/>
@@ -3954,11 +3959,11 @@
       </c>
       <c r="L20" s="126">
         <f t="shared" si="2"/>
-        <v>326917.12</v>
+        <v>360588.12</v>
       </c>
       <c r="M20" s="127">
         <f t="shared" si="3"/>
-        <v>336725.12</v>
+        <v>371406.12</v>
       </c>
       <c r="N20" s="42">
         <f t="shared" si="8"/>
@@ -3985,7 +3990,7 @@
       <c r="F21" s="122">
         <v>186280.13</v>
       </c>
-      <c r="G21" s="190">
+      <c r="G21" s="131">
         <f>F21</f>
         <v>186280.13</v>
       </c>
@@ -3999,7 +4004,7 @@
       </c>
       <c r="J21" s="124">
         <f t="shared" si="5"/>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K21" s="125">
         <f t="shared" si="6"/>
@@ -4007,11 +4012,11 @@
       </c>
       <c r="L21" s="126">
         <f t="shared" si="2"/>
-        <v>186280.13</v>
+        <v>204908.13</v>
       </c>
       <c r="M21" s="127">
         <f t="shared" si="3"/>
-        <v>191868.13</v>
+        <v>211055.13</v>
       </c>
       <c r="N21" s="42">
         <f t="shared" si="8"/>
@@ -4038,7 +4043,7 @@
       <c r="F22" s="122">
         <v>160211.14000000001</v>
       </c>
-      <c r="G22" s="190">
+      <c r="G22" s="131">
         <f>F22</f>
         <v>160211.14000000001</v>
       </c>
@@ -4052,7 +4057,7 @@
       </c>
       <c r="J22" s="124">
         <f t="shared" si="5"/>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K22" s="125">
         <f t="shared" si="6"/>
@@ -4060,11 +4065,11 @@
       </c>
       <c r="L22" s="126">
         <f t="shared" si="2"/>
-        <v>160211.14000000001</v>
+        <v>176233.14</v>
       </c>
       <c r="M22" s="127">
         <f t="shared" si="3"/>
-        <v>165017.14000000001</v>
+        <v>181520.14</v>
       </c>
       <c r="N22" s="42">
         <f t="shared" si="8"/>
@@ -4092,7 +4097,7 @@
       <c r="F23" s="131">
         <v>336716.15</v>
       </c>
-      <c r="G23" s="190">
+      <c r="G23" s="131">
         <f>F23</f>
         <v>336716.15</v>
       </c>
@@ -4106,7 +4111,7 @@
       </c>
       <c r="J23" s="124">
         <f t="shared" si="5"/>
-        <v>336715.54022000002</v>
+        <v>370387.09424199996</v>
       </c>
       <c r="K23" s="125">
         <f t="shared" si="6"/>
@@ -4114,11 +4119,11 @@
       </c>
       <c r="L23" s="126">
         <f t="shared" si="2"/>
-        <v>336716.15</v>
+        <v>370387.15</v>
       </c>
       <c r="M23" s="127">
         <f t="shared" si="3"/>
-        <v>346817.15</v>
+        <v>381499.15</v>
       </c>
       <c r="N23" s="42">
         <f t="shared" si="8"/>
@@ -4143,7 +4148,7 @@
       <c r="F24" s="122">
         <v>180692.16</v>
       </c>
-      <c r="G24" s="190">
+      <c r="G24" s="131">
         <v>186113.16</v>
       </c>
       <c r="H24" s="123">
@@ -4156,7 +4161,7 @@
       </c>
       <c r="J24" s="124">
         <f t="shared" si="5"/>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K24" s="125">
         <f t="shared" si="6"/>
@@ -4164,11 +4169,11 @@
       </c>
       <c r="L24" s="126">
         <f t="shared" si="2"/>
-        <v>180859.16</v>
+        <v>199487.16</v>
       </c>
       <c r="M24" s="127">
         <f t="shared" si="3"/>
-        <v>186285.16</v>
+        <v>205472.16</v>
       </c>
       <c r="N24" s="42">
         <f t="shared" si="8"/>
@@ -4195,7 +4200,7 @@
       <c r="F25" s="131">
         <v>160211.17000000001</v>
       </c>
-      <c r="G25" s="190">
+      <c r="G25" s="131">
         <f>F25</f>
         <v>160211.17000000001</v>
       </c>
@@ -4209,7 +4214,7 @@
       </c>
       <c r="J25" s="124">
         <f t="shared" si="5"/>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K25" s="125">
         <f t="shared" si="6"/>
@@ -4217,11 +4222,11 @@
       </c>
       <c r="L25" s="126">
         <f t="shared" si="2"/>
-        <v>160211.17000000001</v>
+        <v>176233.17</v>
       </c>
       <c r="M25" s="127">
         <f t="shared" si="3"/>
-        <v>165017.17000000001</v>
+        <v>181520.17</v>
       </c>
       <c r="N25" s="42">
         <f t="shared" si="8"/>
@@ -4247,7 +4252,7 @@
       <c r="F26" s="131">
         <v>336716.18</v>
       </c>
-      <c r="G26" s="189">
+      <c r="G26" s="133">
         <f>F26</f>
         <v>336716.18</v>
       </c>
@@ -4261,7 +4266,7 @@
       </c>
       <c r="J26" s="124">
         <f t="shared" si="5"/>
-        <v>336715.54022000002</v>
+        <v>370387.09424199996</v>
       </c>
       <c r="K26" s="125">
         <f t="shared" si="6"/>
@@ -4269,11 +4274,11 @@
       </c>
       <c r="L26" s="126">
         <f t="shared" si="2"/>
-        <v>336716.18</v>
+        <v>370387.18</v>
       </c>
       <c r="M26" s="127">
         <f t="shared" si="3"/>
-        <v>346817.18</v>
+        <v>381499.18</v>
       </c>
       <c r="N26" s="42">
         <f t="shared" si="8"/>
@@ -4311,7 +4316,7 @@
       </c>
       <c r="J27" s="124">
         <f t="shared" si="5"/>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K27" s="125">
         <f t="shared" si="6"/>
@@ -4319,11 +4324,11 @@
       </c>
       <c r="L27" s="126">
         <f t="shared" si="2"/>
-        <v>1078615.19</v>
+        <v>1097243.19</v>
       </c>
       <c r="M27" s="127">
         <f t="shared" si="3"/>
-        <v>1110973.19</v>
+        <v>1130160.19</v>
       </c>
       <c r="N27" s="42">
         <f t="shared" si="8"/>
@@ -4350,7 +4355,7 @@
       <c r="F28" s="133">
         <v>160211.20000000001</v>
       </c>
-      <c r="G28" s="190">
+      <c r="G28" s="131">
         <f t="shared" ref="G28" si="9">F28</f>
         <v>160211.20000000001</v>
       </c>
@@ -4364,7 +4369,7 @@
       </c>
       <c r="J28" s="124">
         <f t="shared" si="5"/>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K28" s="125">
         <f t="shared" si="6"/>
@@ -4372,11 +4377,11 @@
       </c>
       <c r="L28" s="126">
         <f t="shared" si="2"/>
-        <v>160211.20000000001</v>
+        <v>176233.2</v>
       </c>
       <c r="M28" s="127">
         <f t="shared" si="3"/>
-        <v>165017.20000000001</v>
+        <v>181520.2</v>
       </c>
       <c r="N28" s="42">
         <f t="shared" si="8"/>
@@ -4402,7 +4407,7 @@
       <c r="F29" s="133">
         <v>326829.21000000002</v>
       </c>
-      <c r="G29" s="190">
+      <c r="G29" s="131">
         <v>336634.21</v>
       </c>
       <c r="H29" s="123">
@@ -4415,7 +4420,7 @@
       </c>
       <c r="J29" s="124">
         <f t="shared" si="5"/>
-        <v>336715.54022000002</v>
+        <v>370387.09424199996</v>
       </c>
       <c r="K29" s="125">
         <f t="shared" si="6"/>
@@ -4423,11 +4428,11 @@
       </c>
       <c r="L29" s="126">
         <f t="shared" si="2"/>
-        <v>326911.21000000002</v>
+        <v>360582.21</v>
       </c>
       <c r="M29" s="127">
         <f t="shared" si="3"/>
-        <v>336718.21</v>
+        <v>371399.21</v>
       </c>
       <c r="N29" s="42">
         <f t="shared" si="8"/>
@@ -4454,7 +4459,7 @@
       <c r="F30" s="133">
         <v>372432.22</v>
       </c>
-      <c r="G30" s="189">
+      <c r="G30" s="133">
         <v>160000</v>
       </c>
       <c r="H30" s="123">
@@ -4467,7 +4472,7 @@
       </c>
       <c r="J30" s="124">
         <f t="shared" si="5"/>
-        <v>186279.72628300005</v>
+        <v>204907.69891130002</v>
       </c>
       <c r="K30" s="125">
         <f t="shared" si="6"/>
@@ -4475,11 +4480,11 @@
       </c>
       <c r="L30" s="126">
         <f t="shared" si="2"/>
-        <v>405085.22</v>
+        <v>423713.22</v>
       </c>
       <c r="M30" s="127">
         <f t="shared" si="3"/>
-        <v>417238.22</v>
+        <v>436424.22</v>
       </c>
       <c r="N30" s="42">
         <f t="shared" si="8"/>
@@ -4506,7 +4511,7 @@
       <c r="F31" s="133">
         <v>165017.23000000001</v>
       </c>
-      <c r="G31" s="189">
+      <c r="G31" s="133">
         <f>F31</f>
         <v>165017.23000000001</v>
       </c>
@@ -4520,7 +4525,7 @@
       </c>
       <c r="J31" s="124">
         <f t="shared" si="5"/>
-        <v>160211.42639500002</v>
+        <v>176232.56903450002</v>
       </c>
       <c r="K31" s="125">
         <f t="shared" si="6"/>
@@ -4528,11 +4533,11 @@
       </c>
       <c r="L31" s="126">
         <f t="shared" si="2"/>
-        <v>160211.23000000001</v>
+        <v>176233.23</v>
       </c>
       <c r="M31" s="127">
         <f t="shared" si="3"/>
-        <v>165017.23000000001</v>
+        <v>181520.23</v>
       </c>
       <c r="N31" s="42">
         <f t="shared" si="8"/>
@@ -4557,7 +4562,7 @@
       <c r="F32" s="132">
         <v>308475.24</v>
       </c>
-      <c r="G32" s="189">
+      <c r="G32" s="133">
         <f>F32</f>
         <v>308475.24</v>
       </c>
@@ -4571,7 +4576,7 @@
       </c>
       <c r="J32" s="124">
         <f t="shared" si="5"/>
-        <v>308474.88200799999</v>
+        <v>339322.37020879996</v>
       </c>
       <c r="K32" s="125">
         <f t="shared" si="6"/>
@@ -4579,11 +4584,11 @@
       </c>
       <c r="L32" s="126">
         <f t="shared" si="2"/>
-        <v>308475.24</v>
+        <v>339322.24</v>
       </c>
       <c r="M32" s="127">
         <f t="shared" si="3"/>
-        <v>317729.24</v>
+        <v>349502.24</v>
       </c>
       <c r="N32" s="42">
         <f t="shared" si="8"/>
@@ -4591,8 +4596,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="223"/>
-      <c r="B33" s="224"/>
+      <c r="A33" s="221"/>
+      <c r="B33" s="222"/>
       <c r="C33" s="135"/>
       <c r="D33" s="135"/>
       <c r="E33" s="121"/>
@@ -4607,11 +4612,11 @@
       <c r="N33" s="42"/>
     </row>
     <row r="34" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="225" t="s">
+      <c r="A34" s="223" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="225"/>
-      <c r="C34" s="226"/>
+      <c r="B34" s="223"/>
+      <c r="C34" s="224"/>
       <c r="D34" s="137"/>
       <c r="E34" s="145">
         <f t="shared" ref="E34:K34" si="10">SUM(E9:E33)</f>
@@ -4619,23 +4624,23 @@
       </c>
       <c r="F34" s="138">
         <f t="shared" si="10"/>
-        <v>6591208.0000000009</v>
+        <v>6598232.9300000006</v>
       </c>
       <c r="G34" s="139">
         <f t="shared" si="10"/>
-        <v>4865621.3400000017</v>
+        <v>5106822.3400000017</v>
       </c>
       <c r="H34" s="139">
         <f t="shared" si="10"/>
-        <v>1725586.66</v>
+        <v>1491410.59</v>
       </c>
       <c r="I34" s="139">
         <f t="shared" si="10"/>
-        <v>52860.226799999997</v>
+        <v>45834.944699999993</v>
       </c>
       <c r="J34" s="140">
         <f t="shared" si="10"/>
-        <v>5414603.1225699997</v>
+        <v>5956063.4348269999</v>
       </c>
       <c r="K34" s="139">
         <f t="shared" si="10"/>
@@ -4643,11 +4648,11 @@
       </c>
       <c r="L34" s="141">
         <f>SUM(L9:L26)</f>
-        <v>4753543.71</v>
+        <v>4919988.71</v>
       </c>
       <c r="M34" s="141">
         <f>SUM(M9:M33)</f>
-        <v>7408841.0000000009</v>
+        <v>7718117.0000000009</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4656,79 +4661,79 @@
     </row>
     <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="193" t="str">
+      <c r="C37" s="191" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D37" s="193"/>
-      <c r="E37" s="193"/>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="193"/>
-      <c r="L37" s="193"/>
+      <c r="D37" s="191"/>
+      <c r="E37" s="191"/>
+      <c r="F37" s="191"/>
+      <c r="G37" s="191"/>
+      <c r="H37" s="191"/>
+      <c r="I37" s="191"/>
+      <c r="J37" s="191"/>
+      <c r="K37" s="191"/>
+      <c r="L37" s="191"/>
     </row>
     <row r="38" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="193"/>
-      <c r="D38" s="193"/>
-      <c r="E38" s="193"/>
-      <c r="F38" s="193"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
-      <c r="I38" s="193"/>
-      <c r="J38" s="193"/>
-      <c r="K38" s="193"/>
-      <c r="L38" s="193"/>
+      <c r="C38" s="191"/>
+      <c r="D38" s="191"/>
+      <c r="E38" s="191"/>
+      <c r="F38" s="191"/>
+      <c r="G38" s="191"/>
+      <c r="H38" s="191"/>
+      <c r="I38" s="191"/>
+      <c r="J38" s="191"/>
+      <c r="K38" s="191"/>
+      <c r="L38" s="191"/>
     </row>
     <row r="39" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="193"/>
-      <c r="D39" s="193"/>
-      <c r="E39" s="193"/>
-      <c r="F39" s="193"/>
-      <c r="G39" s="193"/>
-      <c r="H39" s="193"/>
-      <c r="I39" s="193"/>
-      <c r="J39" s="193"/>
-      <c r="K39" s="193"/>
-      <c r="L39" s="193"/>
+      <c r="C39" s="191"/>
+      <c r="D39" s="191"/>
+      <c r="E39" s="191"/>
+      <c r="F39" s="191"/>
+      <c r="G39" s="191"/>
+      <c r="H39" s="191"/>
+      <c r="I39" s="191"/>
+      <c r="J39" s="191"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
     </row>
     <row r="40" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="193"/>
-      <c r="D40" s="193"/>
-      <c r="E40" s="193"/>
-      <c r="F40" s="193"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="193"/>
-      <c r="J40" s="193"/>
-      <c r="K40" s="193"/>
-      <c r="L40" s="193"/>
+      <c r="C40" s="191"/>
+      <c r="D40" s="191"/>
+      <c r="E40" s="191"/>
+      <c r="F40" s="191"/>
+      <c r="G40" s="191"/>
+      <c r="H40" s="191"/>
+      <c r="I40" s="191"/>
+      <c r="J40" s="191"/>
+      <c r="K40" s="191"/>
+      <c r="L40" s="191"/>
     </row>
     <row r="41" spans="1:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="193"/>
-      <c r="D41" s="193"/>
-      <c r="E41" s="193"/>
-      <c r="F41" s="193"/>
-      <c r="G41" s="193"/>
-      <c r="H41" s="193"/>
-      <c r="I41" s="193"/>
-      <c r="J41" s="193"/>
-      <c r="K41" s="193"/>
-      <c r="L41" s="193"/>
+      <c r="C41" s="191"/>
+      <c r="D41" s="191"/>
+      <c r="E41" s="191"/>
+      <c r="F41" s="191"/>
+      <c r="G41" s="191"/>
+      <c r="H41" s="191"/>
+      <c r="I41" s="191"/>
+      <c r="J41" s="191"/>
+      <c r="K41" s="191"/>
+      <c r="L41" s="191"/>
     </row>
     <row r="42" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="193"/>
-      <c r="D42" s="193"/>
-      <c r="E42" s="193"/>
-      <c r="F42" s="193"/>
-      <c r="G42" s="193"/>
-      <c r="H42" s="193"/>
-      <c r="I42" s="193"/>
-      <c r="J42" s="193"/>
-      <c r="K42" s="193"/>
-      <c r="L42" s="193"/>
+      <c r="C42" s="191"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="191"/>
+      <c r="F42" s="191"/>
+      <c r="G42" s="191"/>
+      <c r="H42" s="191"/>
+      <c r="I42" s="191"/>
+      <c r="J42" s="191"/>
+      <c r="K42" s="191"/>
+      <c r="L42" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4783,36 +4788,36 @@
       <c r="G5" s="173"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="227"/>
-      <c r="C6" s="228"/>
-      <c r="D6" s="228"/>
-      <c r="E6" s="228"/>
-      <c r="F6" s="228"/>
-      <c r="G6" s="229"/>
+      <c r="B6" s="225"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="227"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="227"/>
-      <c r="C7" s="228"/>
-      <c r="D7" s="228"/>
-      <c r="E7" s="228"/>
-      <c r="F7" s="228"/>
-      <c r="G7" s="229"/>
+      <c r="B7" s="225"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="227"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="227"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="228"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="229"/>
+      <c r="B8" s="225"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
+      <c r="G8" s="227"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="230"/>
-      <c r="C9" s="231"/>
-      <c r="D9" s="231"/>
-      <c r="E9" s="231"/>
-      <c r="F9" s="231"/>
-      <c r="G9" s="232"/>
+      <c r="B9" s="228"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="1">
